--- a/samples/clean-model.xlsx
+++ b/samples/clean-model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nyank\Desktop\後藤さんのclaude\ai-builders-2026\gridlint\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1E7890E-0707-42C2-9BB1-CD20365B64D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE4FA020-0E6B-44E4-8F0E-B1F2E949AF78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8D1287F9-B29F-4DD9-8CD2-B1A3177F19C0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3BEBF9EB-568F-4414-9E93-77999B7C5FDA}"/>
   </bookViews>
   <sheets>
     <sheet name="Operating Model" sheetId="2" r:id="rId1"/>
@@ -573,7 +573,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7DF7567-16CC-4D7F-80FC-DF9D4382AFC0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F611B201-408D-49BF-8840-5B05A70A3ACC}">
   <dimension ref="A1:N29"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -1282,7 +1282,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B2198ED-1B7B-41F4-99B8-DDF12844DD34}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{789FB0C1-713B-4D0C-B518-53728DAF1B9D}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
